--- a/tools/importer/reports/import-section-interior.report.xlsx
+++ b/tools/importer/reports/import-section-interior.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="266">
   <si>
     <t>_reportFile</t>
   </si>
@@ -151,7 +151,7 @@
     <t>nav</t>
   </si>
   <si>
-    <t>2026-10-07T16:47:57.765Z</t>
+    <t>2026-10-07T18:44:48.172Z</t>
   </si>
   <si>
     <t>rc.report.json</t>
@@ -750,6 +750,63 @@
   </si>
   <si>
     <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/what-are-the-liberal-arts-.html</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/academics.report.json</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/academics</t>
+  </si>
+  <si>
+    <t>2026-10-07T19:32:16.787Z</t>
+  </si>
+  <si>
+    <t>Academics | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/academics.html</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/admissions-and-requirements.report.json</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/admissions-and-requirements</t>
+  </si>
+  <si>
+    <t>2026-10-07T19:32:14.782Z</t>
+  </si>
+  <si>
+    <t>Admissions and Requirements | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/admissions-and-requirements.html</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/admitted-students.report.json</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/admitted-students</t>
+  </si>
+  <si>
+    <t>2026-10-07T19:32:22.618Z</t>
+  </si>
+  <si>
+    <t>Admitted Students | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/admitted-students.html</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/student-life.report.json</t>
+  </si>
+  <si>
+    <t>lsa/prospective-students/international/visiting-international/student-life</t>
+  </si>
+  <si>
+    <t>2026-10-07T19:32:19.854Z</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/student-life.html</t>
   </si>
   <si>
     <t>lsa/prospective-students/undergraduate/admissions/undergraduate-application.report.json</t>
@@ -1153,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -2774,6 +2831,146 @@
         <v>246</v>
       </c>
     </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>247</v>
+      </c>
+      <c r="B47" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" t="s">
+        <v>248</v>
+      </c>
+      <c r="G47" t="s">
+        <v>15</v>
+      </c>
+      <c r="H47" t="s">
+        <v>102</v>
+      </c>
+      <c r="I47" t="s">
+        <v>249</v>
+      </c>
+      <c r="J47" t="s">
+        <v>250</v>
+      </c>
+      <c r="K47" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>252</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" t="s">
+        <v>253</v>
+      </c>
+      <c r="G48" t="s">
+        <v>15</v>
+      </c>
+      <c r="H48" t="s">
+        <v>102</v>
+      </c>
+      <c r="I48" t="s">
+        <v>254</v>
+      </c>
+      <c r="J48" t="s">
+        <v>255</v>
+      </c>
+      <c r="K48" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" t="s">
+        <v>12</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" t="s">
+        <v>258</v>
+      </c>
+      <c r="G49" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" t="s">
+        <v>102</v>
+      </c>
+      <c r="I49" t="s">
+        <v>259</v>
+      </c>
+      <c r="J49" t="s">
+        <v>235</v>
+      </c>
+      <c r="K49" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>261</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
+        <v>262</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
+        <v>102</v>
+      </c>
+      <c r="I50" t="s">
+        <v>263</v>
+      </c>
+      <c r="J50" t="s">
+        <v>264</v>
+      </c>
+      <c r="K50" t="s">
+        <v>265</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tools/importer/reports/import-section-interior.report.xlsx
+++ b/tools/importer/reports/import-section-interior.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1012" uniqueCount="392">
   <si>
     <t>_reportFile</t>
   </si>
@@ -175,13 +175,52 @@
     <t>https://lsa.umich.edu/rc</t>
   </si>
   <si>
+    <t>en/about.report.json</t>
+  </si>
+  <si>
+    <t>["hero","columns","columns","columns","columns","columns","cards"]</t>
+  </si>
+  <si>
+    <t>en/about</t>
+  </si>
+  <si>
+    <t>about</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:08.323Z</t>
+  </si>
+  <si>
+    <t>About | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/about.html</t>
+  </si>
+  <si>
+    <t>en/cgis.report.json</t>
+  </si>
+  <si>
+    <t>en/cgis</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:43.411Z</t>
+  </si>
+  <si>
     <t>en/footer.report.json</t>
   </si>
   <si>
     <t>en/footer</t>
   </si>
   <si>
-    <t>2026-10-07T15:47:50.687Z</t>
+    <t>2026-10-08T13:09:00.952Z</t>
+  </si>
+  <si>
+    <t>en/index.report.json</t>
+  </si>
+  <si>
+    <t>en/index</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:08:47.940Z</t>
   </si>
   <si>
     <t>en/nav.report.json</t>
@@ -190,7 +229,37 @@
     <t>en/nav</t>
   </si>
   <si>
-    <t>2026-10-07T15:47:46.487Z</t>
+    <t>2026-10-08T13:08:55.098Z</t>
+  </si>
+  <si>
+    <t>en/prospective-students.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","hero","hero","hero","hero","cards","cards","cards","cards","cards","cards","cards","columns"]</t>
+  </si>
+  <si>
+    <t>en/prospective-students</t>
+  </si>
+  <si>
+    <t>audience-landing</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:25.536Z</t>
+  </si>
+  <si>
+    <t>Prospective Students | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students.html</t>
+  </si>
+  <si>
+    <t>en/rc.report.json</t>
+  </si>
+  <si>
+    <t>en/rc</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:49.973Z</t>
   </si>
   <si>
     <t>english/undergraduate.report.json</t>
@@ -214,45 +283,21 @@
     <t>lsa/about.report.json</t>
   </si>
   <si>
-    <t>["hero","columns","columns","columns","columns","columns","cards"]</t>
-  </si>
-  <si>
     <t>lsa/about</t>
   </si>
   <si>
-    <t>about</t>
-  </si>
-  <si>
     <t>2026-10-07T16:54:28.368Z</t>
   </si>
   <si>
-    <t>About | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/about.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","hero","hero","hero","hero","cards","cards","cards","cards","cards","cards","cards","columns"]</t>
-  </si>
-  <si>
     <t>lsa/prospective-students</t>
   </si>
   <si>
-    <t>audience-landing</t>
-  </si>
-  <si>
     <t>2026-10-07T16:54:20.230Z</t>
   </si>
   <si>
-    <t>Prospective Students | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students.html</t>
-  </si>
-  <si>
     <t>urop/prospective-students.report.json</t>
   </si>
   <si>
@@ -266,6 +311,168 @@
   </si>
   <si>
     <t>https://lsa.umich.edu/urop/prospective-students.html</t>
+  </si>
+  <si>
+    <t>en/academics/departments-and-units.report.json</t>
+  </si>
+  <si>
+    <t>en/academics/departments-and-units</t>
+  </si>
+  <si>
+    <t>academics-listing</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:19.105Z</t>
+  </si>
+  <si>
+    <t>Departments and Units | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/academics/departments-and-units.html</t>
+  </si>
+  <si>
+    <t>en/academics/majors-minors.report.json</t>
+  </si>
+  <si>
+    <t>en/academics/majors-minors</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:16.299Z</t>
+  </si>
+  <si>
+    <t>Majors and Minors | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/academics/majors-minors.html</t>
+  </si>
+  <si>
+    <t>en/english/undergraduate.report.json</t>
+  </si>
+  <si>
+    <t>en/english/undergraduate</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:35.162Z</t>
+  </si>
+  <si>
+    <t>en/prospective-students/graduate.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/graduate</t>
+  </si>
+  <si>
+    <t>section-interior</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:08.692Z</t>
+  </si>
+  <si>
+    <t>Graduate | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/graduate.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:14.055Z</t>
+  </si>
+  <si>
+    <t>International | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:19.722Z</t>
+  </si>
+  <si>
+    <t>LSA 101: Info for Admitted Students | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:16.999Z</t>
+  </si>
+  <si>
+    <t>Student Stories | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/transfer.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/transfer</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:11.347Z</t>
+  </si>
+  <si>
+    <t>Transfer | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/transfer.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate.report.json</t>
+  </si>
+  <si>
+    <t>["hero","hero","cards","cards","columns"]</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:28.029Z</t>
+  </si>
+  <si>
+    <t>Undergraduate | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/visit-campus.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/visit-campus</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:21.645Z</t>
+  </si>
+  <si>
+    <t>Visit Campus | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/visit-campus.html</t>
+  </si>
+  <si>
+    <t>en/urop/prospective-students.report.json</t>
+  </si>
+  <si>
+    <t>en/urop/prospective-students</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:37.858Z</t>
   </si>
   <si>
     <t>lsa/academics/departments-and-units.html.report.json</t>
@@ -299,18 +506,9 @@
     <t>lsa/academics/departments-and-units</t>
   </si>
   <si>
-    <t>academics-listing</t>
-  </si>
-  <si>
     <t>2026-10-07T15:52:40.889Z</t>
   </si>
   <si>
-    <t>Departments and Units | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/academics/departments-and-units.html</t>
-  </si>
-  <si>
     <t>lsa/academics/majors-minors.report.json</t>
   </si>
   <si>
@@ -320,30 +518,15 @@
     <t>2026-10-07T15:52:38.323Z</t>
   </si>
   <si>
-    <t>Majors and Minors | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/academics/majors-minors.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/graduate.report.json</t>
   </si>
   <si>
     <t>lsa/prospective-students/graduate</t>
   </si>
   <si>
-    <t>section-interior</t>
-  </si>
-  <si>
     <t>2026-10-07T18:31:25.691Z</t>
   </si>
   <si>
-    <t>Graduate | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/graduate.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/international.report.json</t>
   </si>
   <si>
@@ -353,12 +536,6 @@
     <t>2026-10-07T18:31:29.784Z</t>
   </si>
   <si>
-    <t>International | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/international.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/lsa101.report.json</t>
   </si>
   <si>
@@ -368,12 +545,6 @@
     <t>2026-10-07T18:31:34.695Z</t>
   </si>
   <si>
-    <t>LSA 101: Info for Admitted Students | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/student-stories.report.json</t>
   </si>
   <si>
@@ -383,12 +554,6 @@
     <t>2026-10-07T18:31:31.755Z</t>
   </si>
   <si>
-    <t>Student Stories | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/transfer.report.json</t>
   </si>
   <si>
@@ -398,30 +563,15 @@
     <t>2026-10-07T18:31:27.283Z</t>
   </si>
   <si>
-    <t>Transfer | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/transfer.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","cards","cards","columns"]</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate</t>
   </si>
   <si>
     <t>2026-10-07T16:54:22.767Z</t>
   </si>
   <si>
-    <t>Undergraduate | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/visit-campus.report.json</t>
   </si>
   <si>
@@ -431,12 +581,6 @@
     <t>2026-10-07T18:31:36.357Z</t>
   </si>
   <si>
-    <t>Visit Campus | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/visit-campus.html</t>
-  </si>
-  <si>
     <t>psych/prospective-students/undergraduate.report.json</t>
   </si>
   <si>
@@ -452,24 +596,324 @@
     <t>https://lsa.umich.edu/psych/prospective-students/undergraduate.html</t>
   </si>
   <si>
+    <t>en/prospective-students/graduate/applying.report.json</t>
+  </si>
+  <si>
+    <t>["accordion"]</t>
+  </si>
+  <si>
+    <t>en/prospective-students/graduate/applying</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:26.040Z</t>
+  </si>
+  <si>
+    <t>Applying | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/graduate/applying.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/graduate/frequently-asked-questions.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/graduate/frequently-asked-questions</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:32.203Z</t>
+  </si>
+  <si>
+    <t>Frequently Asked Questions | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/graduate/frequently-asked-questions.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/graduate/funding-support.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/graduate/funding-support</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:28.908Z</t>
+  </si>
+  <si>
+    <t>Funding and Support | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/graduate/funding-support.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:34.307Z</t>
+  </si>
+  <si>
+    <t>International Visiting | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/community.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/community</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:54.046Z</t>
+  </si>
+  <si>
+    <t>Community | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/community.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/curriculum.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/curriculum</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:48.511Z</t>
+  </si>
+  <si>
+    <t>Curriculum | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/curriculum.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/events.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/events</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:11:00.759Z</t>
+  </si>
+  <si>
+    <t>Events | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/events.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/faculty-and-research.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/faculty-and-research</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:51.659Z</t>
+  </si>
+  <si>
+    <t>Faculty and Research | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/faculty-and-research.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/opportunities-beyond-the-classroom.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/opportunities-beyond-the-classroom</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:57.500Z</t>
+  </si>
+  <si>
+    <t>Opportunities Beyond the Classroom | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/opportunities-beyond-the-classroom.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/student-ambassadors.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/lsa101/student-ambassadors</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:55.815Z</t>
+  </si>
+  <si>
+    <t>Student Ambassadors | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/student-ambassadors.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/abilene-emerson.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/abilene-emerson</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:41.720Z</t>
+  </si>
+  <si>
+    <t>Abilene Emerson | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/abilene-emerson.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/dhaara-antani.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/dhaara-antani</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:36.826Z</t>
+  </si>
+  <si>
+    <t>Dhaara Antani | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/dhaara-antani.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/harish-kilaru.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/harish-kilaru</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:44.071Z</t>
+  </si>
+  <si>
+    <t>Harish Kilaru | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/harish-kilaru.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/jenna-malzahn.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/jenna-malzahn</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:46.172Z</t>
+  </si>
+  <si>
+    <t>Jenna Malzahn | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/jenna-malzahn.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/kepriah-davis.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/student-stories/kepriah-davis</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:39.655Z</t>
+  </si>
+  <si>
+    <t>Kepriah Davis | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/kepriah-davis.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/admissions.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/admissions</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:03.443Z</t>
+  </si>
+  <si>
+    <t>Admissions | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/admissions.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/curriculum.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/curriculum</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:58.910Z</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/curriculum.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/scholarships-financialaid-tuition.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/scholarships-financialaid-tuition</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:05.778Z</t>
+  </si>
+  <si>
+    <t>Scholarships, Financial Aid, and Tuition | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/scholarships-financialaid-tuition.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/student-life.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/student-life</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:00.983Z</t>
+  </si>
+  <si>
+    <t>Student Life | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/student-life.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/what-are-the-liberal-arts.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/what-are-the-liberal-arts</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:56.143Z</t>
+  </si>
+  <si>
+    <t>What Are the Liberal Arts? | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/what-are-the-liberal-arts-.html</t>
+  </si>
+  <si>
+    <t>en/psych/prospective-students/undergraduate.report.json</t>
+  </si>
+  <si>
+    <t>en/psych/prospective-students/undergraduate</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:09:40.219Z</t>
+  </si>
+  <si>
     <t>lsa/prospective-students/graduate/applying.report.json</t>
   </si>
   <si>
-    <t>["accordion"]</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/graduate/applying</t>
   </si>
   <si>
     <t>2026-10-07T18:31:40.832Z</t>
   </si>
   <si>
-    <t>Applying | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/graduate/applying.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/graduate/frequently-asked-questions.report.json</t>
   </si>
   <si>
@@ -479,12 +923,6 @@
     <t>2026-10-07T18:31:45.514Z</t>
   </si>
   <si>
-    <t>Frequently Asked Questions | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/graduate/frequently-asked-questions.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/graduate/funding-support.report.json</t>
   </si>
   <si>
@@ -494,12 +932,6 @@
     <t>2026-10-07T18:31:43.327Z</t>
   </si>
   <si>
-    <t>Funding and Support | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/graduate/funding-support.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/international/visiting-international.report.json</t>
   </si>
   <si>
@@ -509,12 +941,6 @@
     <t>2026-10-07T18:31:48.167Z</t>
   </si>
   <si>
-    <t>International Visiting | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/lsa101/community.report.json</t>
   </si>
   <si>
@@ -524,12 +950,6 @@
     <t>2026-10-07T18:32:06.118Z</t>
   </si>
   <si>
-    <t>Community | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/community.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/lsa101/curriculum.report.json</t>
   </si>
   <si>
@@ -539,12 +959,6 @@
     <t>2026-10-07T18:32:02.247Z</t>
   </si>
   <si>
-    <t>Curriculum | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/curriculum.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/lsa101/events.report.json</t>
   </si>
   <si>
@@ -554,12 +968,6 @@
     <t>2026-10-07T18:32:13.487Z</t>
   </si>
   <si>
-    <t>Events | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/events.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/lsa101/faculty-and-research.report.json</t>
   </si>
   <si>
@@ -569,12 +977,6 @@
     <t>2026-10-07T18:32:04.295Z</t>
   </si>
   <si>
-    <t>Faculty and Research | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/faculty-and-research.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/lsa101/opportunities-beyond-the-classroom.report.json</t>
   </si>
   <si>
@@ -584,12 +986,6 @@
     <t>2026-10-07T18:32:11.815Z</t>
   </si>
   <si>
-    <t>Opportunities Beyond the Classroom | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/opportunities-beyond-the-classroom.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/lsa101/student-ambassadors.report.json</t>
   </si>
   <si>
@@ -599,12 +995,6 @@
     <t>2026-10-07T18:32:09.024Z</t>
   </si>
   <si>
-    <t>Student Ambassadors | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/lsa101/student-ambassadors.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/student-stories/abilene-emerson.report.json</t>
   </si>
   <si>
@@ -614,12 +1004,6 @@
     <t>2026-10-07T18:31:55.923Z</t>
   </si>
   <si>
-    <t>Abilene Emerson | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/abilene-emerson.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/student-stories/dhaara-antani.report.json</t>
   </si>
   <si>
@@ -629,12 +1013,6 @@
     <t>2026-10-07T18:31:50.332Z</t>
   </si>
   <si>
-    <t>Dhaara Antani | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/dhaara-antani.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/student-stories/harish-kilaru.report.json</t>
   </si>
   <si>
@@ -644,12 +1022,6 @@
     <t>2026-10-07T18:31:57.858Z</t>
   </si>
   <si>
-    <t>Harish Kilaru | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/harish-kilaru.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/student-stories/jenna-malzahn.report.json</t>
   </si>
   <si>
@@ -659,12 +1031,6 @@
     <t>2026-10-07T18:31:59.941Z</t>
   </si>
   <si>
-    <t>Jenna Malzahn | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/jenna-malzahn.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/student-stories/kepriah-davis.report.json</t>
   </si>
   <si>
@@ -674,12 +1040,6 @@
     <t>2026-10-07T18:31:53.447Z</t>
   </si>
   <si>
-    <t>Kepriah Davis | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/student-stories/kepriah-davis.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate/admissions.report.json</t>
   </si>
   <si>
@@ -689,12 +1049,6 @@
     <t>2026-10-07T18:31:21.313Z</t>
   </si>
   <si>
-    <t>Admissions | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/admissions.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate/curriculum.report.json</t>
   </si>
   <si>
@@ -704,9 +1058,6 @@
     <t>2026-10-07T18:31:17.106Z</t>
   </si>
   <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/curriculum.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate/scholarships-financialaid-tuition.report.json</t>
   </si>
   <si>
@@ -716,12 +1067,6 @@
     <t>2026-10-07T18:31:23.393Z</t>
   </si>
   <si>
-    <t>Scholarships, Financial Aid, and Tuition | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/scholarships-financialaid-tuition.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate/student-life.report.json</t>
   </si>
   <si>
@@ -731,12 +1076,6 @@
     <t>2026-10-07T18:31:19.185Z</t>
   </si>
   <si>
-    <t>Student Life | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/student-life.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate/what-are-the-liberal-arts.report.json</t>
   </si>
   <si>
@@ -746,10 +1085,76 @@
     <t>2026-10-07T18:31:14.633Z</t>
   </si>
   <si>
-    <t>What Are the Liberal Arts? | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/what-are-the-liberal-arts-.html</t>
+    <t>en/prospective-students/international/visiting-international/academics.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international/academics</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:11:05.019Z</t>
+  </si>
+  <si>
+    <t>Academics | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/academics.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international/admissions-and-requirements.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international/admissions-and-requirements</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:11:02.992Z</t>
+  </si>
+  <si>
+    <t>Admissions and Requirements | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/admissions-and-requirements.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international/admitted-students.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international/admitted-students</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:11:09.362Z</t>
+  </si>
+  <si>
+    <t>Admitted Students | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/admitted-students.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international/student-life.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/international/visiting-international/student-life</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:11:06.906Z</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/student-life.html</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/admissions/undergraduate-application.report.json</t>
+  </si>
+  <si>
+    <t>en/prospective-students/undergraduate/admissions/undergraduate-application</t>
+  </si>
+  <si>
+    <t>2026-10-08T13:10:24.018Z</t>
+  </si>
+  <si>
+    <t>Undergraduate Application | U-M LSA U-M College of LSA</t>
+  </si>
+  <si>
+    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/admissions/undergraduate-application.html</t>
   </si>
   <si>
     <t>lsa/prospective-students/international/visiting-international/academics.report.json</t>
@@ -761,12 +1166,6 @@
     <t>2026-10-07T19:32:16.787Z</t>
   </si>
   <si>
-    <t>Academics | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/academics.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/international/visiting-international/admissions-and-requirements.report.json</t>
   </si>
   <si>
@@ -776,12 +1175,6 @@
     <t>2026-10-07T19:32:14.782Z</t>
   </si>
   <si>
-    <t>Admissions and Requirements | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/admissions-and-requirements.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/international/visiting-international/admitted-students.report.json</t>
   </si>
   <si>
@@ -791,12 +1184,6 @@
     <t>2026-10-07T19:32:22.618Z</t>
   </si>
   <si>
-    <t>Admitted Students | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/admitted-students.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/international/visiting-international/student-life.report.json</t>
   </si>
   <si>
@@ -806,9 +1193,6 @@
     <t>2026-10-07T19:32:19.854Z</t>
   </si>
   <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/international/visiting-international/student-life.html</t>
-  </si>
-  <si>
     <t>lsa/prospective-students/undergraduate/admissions/undergraduate-application.report.json</t>
   </si>
   <si>
@@ -816,12 +1200,6 @@
   </si>
   <si>
     <t>2026-10-07T18:31:39.165Z</t>
-  </si>
-  <si>
-    <t>Undergraduate Application | U-M LSA U-M College of LSA</t>
-  </si>
-  <si>
-    <t>https://lsa.umich.edu/lsa/prospective-students/undergraduate/admissions/undergraduate-application.html</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K50"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -1506,7 +1884,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -1515,33 +1893,33 @@
         <v>13</v>
       </c>
       <c r="E9" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="I9" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J9" t="s">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="K9" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" t="s">
         <v>13</v>
@@ -1550,33 +1928,33 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J10" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="K10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
         <v>13</v>
@@ -1585,33 +1963,33 @@
         <v>13</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J11" t="s">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="K11" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -1629,24 +2007,24 @@
         <v>15</v>
       </c>
       <c r="H12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" t="s">
         <v>67</v>
       </c>
-      <c r="I12" t="s">
-        <v>68</v>
-      </c>
       <c r="J12" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="K12" t="s">
-        <v>70</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="C13" t="s">
         <v>13</v>
@@ -1655,33 +2033,33 @@
         <v>13</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
       </c>
       <c r="H13" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="I13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="K13" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -1693,65 +2071,65 @@
         <v>13</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
       </c>
       <c r="H14" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="I14" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J14" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="E15" t="s">
         <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="I15" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="K15" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C16" t="s">
         <v>13</v>
@@ -1763,30 +2141,30 @@
         <v>13</v>
       </c>
       <c r="F16" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="I16" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="J16" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="K16" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
         <v>13</v>
@@ -1798,30 +2176,30 @@
         <v>13</v>
       </c>
       <c r="F17" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="I17" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>98</v>
+        <v>57</v>
       </c>
       <c r="K17" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B18" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="C18" t="s">
         <v>13</v>
@@ -1833,27 +2211,27 @@
         <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
       </c>
       <c r="H18" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="I18" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="J18" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="K18" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
         <v>12</v>
@@ -1868,27 +2246,27 @@
         <v>13</v>
       </c>
       <c r="F19" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
       </c>
       <c r="H19" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="I19" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="J19" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="K19" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
         <v>12</v>
@@ -1903,30 +2281,30 @@
         <v>13</v>
       </c>
       <c r="F20" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
       </c>
       <c r="H20" t="s">
+        <v>100</v>
+      </c>
+      <c r="I20" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20" t="s">
         <v>102</v>
       </c>
-      <c r="I20" t="s">
-        <v>113</v>
-      </c>
-      <c r="J20" t="s">
-        <v>114</v>
-      </c>
       <c r="K20" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="B21" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
@@ -1938,30 +2316,30 @@
         <v>13</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
       </c>
       <c r="H21" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I21" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="J21" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="K21" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
         <v>13</v>
@@ -1973,30 +2351,30 @@
         <v>13</v>
       </c>
       <c r="F22" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="G22" t="s">
         <v>15</v>
       </c>
       <c r="H22" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="I22" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="J22" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="K22" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
@@ -2008,27 +2386,27 @@
         <v>13</v>
       </c>
       <c r="F23" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="G23" t="s">
         <v>15</v>
       </c>
       <c r="H23" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="I23" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="J23" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="K23" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
@@ -2043,30 +2421,30 @@
         <v>13</v>
       </c>
       <c r="F24" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="G24" t="s">
         <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I24" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="J24" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="K24" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B25" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C25" t="s">
         <v>13</v>
@@ -2078,30 +2456,30 @@
         <v>13</v>
       </c>
       <c r="F25" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="G25" t="s">
         <v>15</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="I25" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="J25" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="K25" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C26" t="s">
         <v>13</v>
@@ -2113,30 +2491,30 @@
         <v>13</v>
       </c>
       <c r="F26" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="G26" t="s">
         <v>15</v>
       </c>
       <c r="H26" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I26" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="J26" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="K26" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B27" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="C27" t="s">
         <v>13</v>
@@ -2148,62 +2526,62 @@
         <v>13</v>
       </c>
       <c r="F27" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="G27" t="s">
         <v>15</v>
       </c>
       <c r="H27" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I27" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="J27" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="K27" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="B28" t="s">
+        <v>139</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" t="s">
+        <v>13</v>
+      </c>
+      <c r="F28" t="s">
+        <v>140</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>74</v>
+      </c>
+      <c r="I28" t="s">
+        <v>141</v>
+      </c>
+      <c r="J28" t="s">
+        <v>142</v>
+      </c>
+      <c r="K28" t="s">
         <v>143</v>
-      </c>
-      <c r="C28" t="s">
-        <v>13</v>
-      </c>
-      <c r="D28" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" t="s">
-        <v>154</v>
-      </c>
-      <c r="G28" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" t="s">
-        <v>102</v>
-      </c>
-      <c r="I28" t="s">
-        <v>155</v>
-      </c>
-      <c r="J28" t="s">
-        <v>156</v>
-      </c>
-      <c r="K28" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
         <v>12</v>
@@ -2218,27 +2596,27 @@
         <v>13</v>
       </c>
       <c r="F29" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="G29" t="s">
         <v>15</v>
       </c>
       <c r="H29" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I29" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="J29" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="K29" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
@@ -2253,62 +2631,62 @@
         <v>13</v>
       </c>
       <c r="F30" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="G30" t="s">
         <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="I30" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="J30" t="s">
-        <v>166</v>
+        <v>96</v>
       </c>
       <c r="K30" t="s">
-        <v>167</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>13</v>
+        <v>153</v>
       </c>
       <c r="D31" t="s">
-        <v>13</v>
+        <v>154</v>
       </c>
       <c r="E31" t="s">
         <v>13</v>
       </c>
       <c r="F31" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="H31" t="s">
-        <v>102</v>
+        <v>13</v>
       </c>
       <c r="I31" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="J31" t="s">
-        <v>171</v>
+        <v>13</v>
       </c>
       <c r="K31" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B32" t="s">
         <v>12</v>
@@ -2323,27 +2701,27 @@
         <v>13</v>
       </c>
       <c r="F32" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="G32" t="s">
         <v>15</v>
       </c>
       <c r="H32" t="s">
+        <v>100</v>
+      </c>
+      <c r="I32" t="s">
+        <v>160</v>
+      </c>
+      <c r="J32" t="s">
         <v>102</v>
       </c>
-      <c r="I32" t="s">
-        <v>175</v>
-      </c>
-      <c r="J32" t="s">
-        <v>176</v>
-      </c>
       <c r="K32" t="s">
-        <v>177</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="B33" t="s">
         <v>12</v>
@@ -2358,30 +2736,30 @@
         <v>13</v>
       </c>
       <c r="F33" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="G33" t="s">
         <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I33" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="J33" t="s">
-        <v>181</v>
+        <v>107</v>
       </c>
       <c r="K33" t="s">
-        <v>182</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C34" t="s">
         <v>13</v>
@@ -2393,27 +2771,27 @@
         <v>13</v>
       </c>
       <c r="F34" t="s">
-        <v>184</v>
+        <v>165</v>
       </c>
       <c r="G34" t="s">
         <v>15</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I34" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="J34" t="s">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="K34" t="s">
-        <v>187</v>
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>188</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -2428,27 +2806,27 @@
         <v>13</v>
       </c>
       <c r="F35" t="s">
-        <v>189</v>
+        <v>168</v>
       </c>
       <c r="G35" t="s">
         <v>15</v>
       </c>
       <c r="H35" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I35" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="J35" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
       <c r="K35" t="s">
-        <v>192</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>193</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
         <v>12</v>
@@ -2463,30 +2841,30 @@
         <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="G36" t="s">
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I36" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="J36" t="s">
-        <v>196</v>
+        <v>126</v>
       </c>
       <c r="K36" t="s">
-        <v>197</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>198</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C37" t="s">
         <v>13</v>
@@ -2498,27 +2876,27 @@
         <v>13</v>
       </c>
       <c r="F37" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="G37" t="s">
         <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I37" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="J37" t="s">
-        <v>201</v>
+        <v>131</v>
       </c>
       <c r="K37" t="s">
-        <v>202</v>
+        <v>132</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>203</v>
+        <v>176</v>
       </c>
       <c r="B38" t="s">
         <v>12</v>
@@ -2533,30 +2911,30 @@
         <v>13</v>
       </c>
       <c r="F38" t="s">
-        <v>204</v>
+        <v>177</v>
       </c>
       <c r="G38" t="s">
         <v>15</v>
       </c>
       <c r="H38" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I38" t="s">
-        <v>205</v>
+        <v>178</v>
       </c>
       <c r="J38" t="s">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="K38" t="s">
-        <v>207</v>
+        <v>137</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>139</v>
       </c>
       <c r="C39" t="s">
         <v>13</v>
@@ -2568,27 +2946,27 @@
         <v>13</v>
       </c>
       <c r="F39" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="G39" t="s">
         <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="I39" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="J39" t="s">
-        <v>211</v>
+        <v>142</v>
       </c>
       <c r="K39" t="s">
-        <v>212</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="B40" t="s">
         <v>12</v>
@@ -2603,30 +2981,30 @@
         <v>13</v>
       </c>
       <c r="F40" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="G40" t="s">
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I40" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="J40" t="s">
-        <v>216</v>
+        <v>147</v>
       </c>
       <c r="K40" t="s">
-        <v>217</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>218</v>
+        <v>185</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>82</v>
       </c>
       <c r="C41" t="s">
         <v>13</v>
@@ -2638,30 +3016,30 @@
         <v>13</v>
       </c>
       <c r="F41" t="s">
-        <v>219</v>
+        <v>186</v>
       </c>
       <c r="G41" t="s">
         <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="I41" t="s">
-        <v>220</v>
+        <v>187</v>
       </c>
       <c r="J41" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="K41" t="s">
-        <v>222</v>
+        <v>189</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>223</v>
+        <v>190</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
@@ -2673,30 +3051,30 @@
         <v>13</v>
       </c>
       <c r="F42" t="s">
-        <v>224</v>
+        <v>192</v>
       </c>
       <c r="G42" t="s">
         <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I42" t="s">
-        <v>225</v>
+        <v>193</v>
       </c>
       <c r="J42" t="s">
-        <v>171</v>
+        <v>194</v>
       </c>
       <c r="K42" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="B43" t="s">
-        <v>59</v>
+        <v>191</v>
       </c>
       <c r="C43" t="s">
         <v>13</v>
@@ -2708,30 +3086,30 @@
         <v>13</v>
       </c>
       <c r="F43" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="G43" t="s">
         <v>15</v>
       </c>
       <c r="H43" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I43" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="J43" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="K43" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>191</v>
       </c>
       <c r="C44" t="s">
         <v>13</v>
@@ -2743,27 +3121,27 @@
         <v>13</v>
       </c>
       <c r="F44" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="G44" t="s">
         <v>15</v>
       </c>
       <c r="H44" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I44" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="J44" t="s">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="K44" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="B45" t="s">
         <v>12</v>
@@ -2778,27 +3156,27 @@
         <v>13</v>
       </c>
       <c r="F45" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="G45" t="s">
         <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I45" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="J45" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="K45" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="B46" t="s">
         <v>12</v>
@@ -2813,30 +3191,30 @@
         <v>13</v>
       </c>
       <c r="F46" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="G46" t="s">
         <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I46" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="J46" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="K46" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="B47" t="s">
-        <v>143</v>
+        <v>12</v>
       </c>
       <c r="C47" t="s">
         <v>13</v>
@@ -2848,27 +3226,27 @@
         <v>13</v>
       </c>
       <c r="F47" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="G47" t="s">
         <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I47" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="J47" t="s">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="K47" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="B48" t="s">
         <v>12</v>
@@ -2883,27 +3261,27 @@
         <v>13</v>
       </c>
       <c r="F48" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="G48" t="s">
         <v>15</v>
       </c>
       <c r="H48" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I48" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="J48" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="K48" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="B49" t="s">
         <v>12</v>
@@ -2918,57 +3296,1527 @@
         <v>13</v>
       </c>
       <c r="F49" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="G49" t="s">
         <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="I49" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="J49" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="K49" t="s">
-        <v>260</v>
+        <v>230</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>231</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>13</v>
+      </c>
+      <c r="F50" t="s">
+        <v>232</v>
+      </c>
+      <c r="G50" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" t="s">
+        <v>114</v>
+      </c>
+      <c r="I50" t="s">
+        <v>233</v>
+      </c>
+      <c r="J50" t="s">
+        <v>234</v>
+      </c>
+      <c r="K50" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>236</v>
+      </c>
+      <c r="B51" t="s">
+        <v>12</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>13</v>
+      </c>
+      <c r="F51" t="s">
+        <v>237</v>
+      </c>
+      <c r="G51" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" t="s">
+        <v>114</v>
+      </c>
+      <c r="I51" t="s">
+        <v>238</v>
+      </c>
+      <c r="J51" t="s">
+        <v>239</v>
+      </c>
+      <c r="K51" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>241</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" t="s">
+        <v>242</v>
+      </c>
+      <c r="G52" t="s">
+        <v>15</v>
+      </c>
+      <c r="H52" t="s">
+        <v>114</v>
+      </c>
+      <c r="I52" t="s">
+        <v>243</v>
+      </c>
+      <c r="J52" t="s">
+        <v>244</v>
+      </c>
+      <c r="K52" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>246</v>
+      </c>
+      <c r="B53" t="s">
+        <v>12</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" t="s">
+        <v>247</v>
+      </c>
+      <c r="G53" t="s">
+        <v>15</v>
+      </c>
+      <c r="H53" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" t="s">
+        <v>248</v>
+      </c>
+      <c r="J53" t="s">
+        <v>249</v>
+      </c>
+      <c r="K53" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>251</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>13</v>
+      </c>
+      <c r="E54" t="s">
+        <v>13</v>
+      </c>
+      <c r="F54" t="s">
+        <v>252</v>
+      </c>
+      <c r="G54" t="s">
+        <v>15</v>
+      </c>
+      <c r="H54" t="s">
+        <v>114</v>
+      </c>
+      <c r="I54" t="s">
+        <v>253</v>
+      </c>
+      <c r="J54" t="s">
+        <v>254</v>
+      </c>
+      <c r="K54" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>256</v>
+      </c>
+      <c r="B55" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>13</v>
+      </c>
+      <c r="E55" t="s">
+        <v>13</v>
+      </c>
+      <c r="F55" t="s">
+        <v>257</v>
+      </c>
+      <c r="G55" t="s">
+        <v>15</v>
+      </c>
+      <c r="H55" t="s">
+        <v>114</v>
+      </c>
+      <c r="I55" t="s">
+        <v>258</v>
+      </c>
+      <c r="J55" t="s">
+        <v>259</v>
+      </c>
+      <c r="K55" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
         <v>261</v>
       </c>
-      <c r="B50" t="s">
-        <v>12</v>
-      </c>
-      <c r="C50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" t="s">
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>13</v>
+      </c>
+      <c r="E56" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" t="s">
         <v>262</v>
       </c>
-      <c r="G50" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" t="s">
-        <v>102</v>
-      </c>
-      <c r="I50" t="s">
+      <c r="G56" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" t="s">
+        <v>114</v>
+      </c>
+      <c r="I56" t="s">
         <v>263</v>
       </c>
-      <c r="J50" t="s">
+      <c r="J56" t="s">
         <v>264</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K56" t="s">
         <v>265</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>266</v>
+      </c>
+      <c r="B57" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>13</v>
+      </c>
+      <c r="E57" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" t="s">
+        <v>267</v>
+      </c>
+      <c r="G57" t="s">
+        <v>15</v>
+      </c>
+      <c r="H57" t="s">
+        <v>114</v>
+      </c>
+      <c r="I57" t="s">
+        <v>268</v>
+      </c>
+      <c r="J57" t="s">
+        <v>269</v>
+      </c>
+      <c r="K57" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>271</v>
+      </c>
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>13</v>
+      </c>
+      <c r="F58" t="s">
+        <v>272</v>
+      </c>
+      <c r="G58" t="s">
+        <v>15</v>
+      </c>
+      <c r="H58" t="s">
+        <v>114</v>
+      </c>
+      <c r="I58" t="s">
+        <v>273</v>
+      </c>
+      <c r="J58" t="s">
+        <v>219</v>
+      </c>
+      <c r="K58" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>275</v>
+      </c>
+      <c r="B59" t="s">
+        <v>82</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" t="s">
+        <v>276</v>
+      </c>
+      <c r="G59" t="s">
+        <v>15</v>
+      </c>
+      <c r="H59" t="s">
+        <v>114</v>
+      </c>
+      <c r="I59" t="s">
+        <v>277</v>
+      </c>
+      <c r="J59" t="s">
+        <v>278</v>
+      </c>
+      <c r="K59" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>280</v>
+      </c>
+      <c r="B60" t="s">
+        <v>12</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" t="s">
+        <v>281</v>
+      </c>
+      <c r="G60" t="s">
+        <v>15</v>
+      </c>
+      <c r="H60" t="s">
+        <v>114</v>
+      </c>
+      <c r="I60" t="s">
+        <v>282</v>
+      </c>
+      <c r="J60" t="s">
+        <v>283</v>
+      </c>
+      <c r="K60" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>285</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
+        <v>286</v>
+      </c>
+      <c r="G61" t="s">
+        <v>15</v>
+      </c>
+      <c r="H61" t="s">
+        <v>114</v>
+      </c>
+      <c r="I61" t="s">
+        <v>287</v>
+      </c>
+      <c r="J61" t="s">
+        <v>288</v>
+      </c>
+      <c r="K61" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>290</v>
+      </c>
+      <c r="B62" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" t="s">
+        <v>291</v>
+      </c>
+      <c r="G62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" t="s">
+        <v>292</v>
+      </c>
+      <c r="J62" t="s">
+        <v>188</v>
+      </c>
+      <c r="K62" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>293</v>
+      </c>
+      <c r="B63" t="s">
+        <v>191</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" t="s">
+        <v>294</v>
+      </c>
+      <c r="G63" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" t="s">
+        <v>114</v>
+      </c>
+      <c r="I63" t="s">
+        <v>295</v>
+      </c>
+      <c r="J63" t="s">
+        <v>194</v>
+      </c>
+      <c r="K63" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>296</v>
+      </c>
+      <c r="B64" t="s">
+        <v>191</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>13</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" t="s">
+        <v>297</v>
+      </c>
+      <c r="G64" t="s">
+        <v>15</v>
+      </c>
+      <c r="H64" t="s">
+        <v>114</v>
+      </c>
+      <c r="I64" t="s">
+        <v>298</v>
+      </c>
+      <c r="J64" t="s">
+        <v>199</v>
+      </c>
+      <c r="K64" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>299</v>
+      </c>
+      <c r="B65" t="s">
+        <v>191</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>13</v>
+      </c>
+      <c r="E65" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" t="s">
+        <v>300</v>
+      </c>
+      <c r="G65" t="s">
+        <v>15</v>
+      </c>
+      <c r="H65" t="s">
+        <v>114</v>
+      </c>
+      <c r="I65" t="s">
+        <v>301</v>
+      </c>
+      <c r="J65" t="s">
+        <v>204</v>
+      </c>
+      <c r="K65" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>302</v>
+      </c>
+      <c r="B66" t="s">
+        <v>12</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>13</v>
+      </c>
+      <c r="E66" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" t="s">
+        <v>303</v>
+      </c>
+      <c r="G66" t="s">
+        <v>15</v>
+      </c>
+      <c r="H66" t="s">
+        <v>114</v>
+      </c>
+      <c r="I66" t="s">
+        <v>304</v>
+      </c>
+      <c r="J66" t="s">
+        <v>209</v>
+      </c>
+      <c r="K66" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>305</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>13</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
+        <v>306</v>
+      </c>
+      <c r="G67" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" t="s">
+        <v>114</v>
+      </c>
+      <c r="I67" t="s">
+        <v>307</v>
+      </c>
+      <c r="J67" t="s">
+        <v>214</v>
+      </c>
+      <c r="K67" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>308</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>13</v>
+      </c>
+      <c r="F68" t="s">
+        <v>309</v>
+      </c>
+      <c r="G68" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" t="s">
+        <v>114</v>
+      </c>
+      <c r="I68" t="s">
+        <v>310</v>
+      </c>
+      <c r="J68" t="s">
+        <v>219</v>
+      </c>
+      <c r="K68" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>311</v>
+      </c>
+      <c r="B69" t="s">
+        <v>12</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>13</v>
+      </c>
+      <c r="F69" t="s">
+        <v>312</v>
+      </c>
+      <c r="G69" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" t="s">
+        <v>114</v>
+      </c>
+      <c r="I69" t="s">
+        <v>313</v>
+      </c>
+      <c r="J69" t="s">
+        <v>224</v>
+      </c>
+      <c r="K69" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>314</v>
+      </c>
+      <c r="B70" t="s">
+        <v>12</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
+        <v>315</v>
+      </c>
+      <c r="G70" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" t="s">
+        <v>114</v>
+      </c>
+      <c r="I70" t="s">
+        <v>316</v>
+      </c>
+      <c r="J70" t="s">
+        <v>229</v>
+      </c>
+      <c r="K70" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>317</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>318</v>
+      </c>
+      <c r="G71" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" t="s">
+        <v>114</v>
+      </c>
+      <c r="I71" t="s">
+        <v>319</v>
+      </c>
+      <c r="J71" t="s">
+        <v>234</v>
+      </c>
+      <c r="K71" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>320</v>
+      </c>
+      <c r="B72" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="E72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>321</v>
+      </c>
+      <c r="G72" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" t="s">
+        <v>114</v>
+      </c>
+      <c r="I72" t="s">
+        <v>322</v>
+      </c>
+      <c r="J72" t="s">
+        <v>239</v>
+      </c>
+      <c r="K72" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>323</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>324</v>
+      </c>
+      <c r="G73" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" t="s">
+        <v>114</v>
+      </c>
+      <c r="I73" t="s">
+        <v>325</v>
+      </c>
+      <c r="J73" t="s">
+        <v>244</v>
+      </c>
+      <c r="K73" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>326</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="E74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>327</v>
+      </c>
+      <c r="G74" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" t="s">
+        <v>114</v>
+      </c>
+      <c r="I74" t="s">
+        <v>328</v>
+      </c>
+      <c r="J74" t="s">
+        <v>249</v>
+      </c>
+      <c r="K74" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>329</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
+        <v>13</v>
+      </c>
+      <c r="E75" t="s">
+        <v>13</v>
+      </c>
+      <c r="F75" t="s">
+        <v>330</v>
+      </c>
+      <c r="G75" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" t="s">
+        <v>114</v>
+      </c>
+      <c r="I75" t="s">
+        <v>331</v>
+      </c>
+      <c r="J75" t="s">
+        <v>254</v>
+      </c>
+      <c r="K75" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>332</v>
+      </c>
+      <c r="B76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
+        <v>333</v>
+      </c>
+      <c r="G76" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" t="s">
+        <v>114</v>
+      </c>
+      <c r="I76" t="s">
+        <v>334</v>
+      </c>
+      <c r="J76" t="s">
+        <v>259</v>
+      </c>
+      <c r="K76" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>335</v>
+      </c>
+      <c r="B77" t="s">
+        <v>12</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>13</v>
+      </c>
+      <c r="F77" t="s">
+        <v>336</v>
+      </c>
+      <c r="G77" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" t="s">
+        <v>114</v>
+      </c>
+      <c r="I77" t="s">
+        <v>337</v>
+      </c>
+      <c r="J77" t="s">
+        <v>264</v>
+      </c>
+      <c r="K77" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>338</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>13</v>
+      </c>
+      <c r="F78" t="s">
+        <v>339</v>
+      </c>
+      <c r="G78" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" t="s">
+        <v>114</v>
+      </c>
+      <c r="I78" t="s">
+        <v>340</v>
+      </c>
+      <c r="J78" t="s">
+        <v>269</v>
+      </c>
+      <c r="K78" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>341</v>
+      </c>
+      <c r="B79" t="s">
+        <v>12</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
+        <v>342</v>
+      </c>
+      <c r="G79" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" t="s">
+        <v>114</v>
+      </c>
+      <c r="I79" t="s">
+        <v>343</v>
+      </c>
+      <c r="J79" t="s">
+        <v>219</v>
+      </c>
+      <c r="K79" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>344</v>
+      </c>
+      <c r="B80" t="s">
+        <v>82</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>13</v>
+      </c>
+      <c r="E80" t="s">
+        <v>13</v>
+      </c>
+      <c r="F80" t="s">
+        <v>345</v>
+      </c>
+      <c r="G80" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" t="s">
+        <v>114</v>
+      </c>
+      <c r="I80" t="s">
+        <v>346</v>
+      </c>
+      <c r="J80" t="s">
+        <v>278</v>
+      </c>
+      <c r="K80" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>347</v>
+      </c>
+      <c r="B81" t="s">
+        <v>12</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s">
+        <v>13</v>
+      </c>
+      <c r="F81" t="s">
+        <v>348</v>
+      </c>
+      <c r="G81" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" t="s">
+        <v>114</v>
+      </c>
+      <c r="I81" t="s">
+        <v>349</v>
+      </c>
+      <c r="J81" t="s">
+        <v>283</v>
+      </c>
+      <c r="K81" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>350</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>13</v>
+      </c>
+      <c r="E82" t="s">
+        <v>13</v>
+      </c>
+      <c r="F82" t="s">
+        <v>351</v>
+      </c>
+      <c r="G82" t="s">
+        <v>15</v>
+      </c>
+      <c r="H82" t="s">
+        <v>114</v>
+      </c>
+      <c r="I82" t="s">
+        <v>352</v>
+      </c>
+      <c r="J82" t="s">
+        <v>288</v>
+      </c>
+      <c r="K82" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>353</v>
+      </c>
+      <c r="B83" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>13</v>
+      </c>
+      <c r="E83" t="s">
+        <v>13</v>
+      </c>
+      <c r="F83" t="s">
+        <v>354</v>
+      </c>
+      <c r="G83" t="s">
+        <v>15</v>
+      </c>
+      <c r="H83" t="s">
+        <v>114</v>
+      </c>
+      <c r="I83" t="s">
+        <v>355</v>
+      </c>
+      <c r="J83" t="s">
+        <v>356</v>
+      </c>
+      <c r="K83" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>358</v>
+      </c>
+      <c r="B84" t="s">
+        <v>191</v>
+      </c>
+      <c r="C84" t="s">
+        <v>13</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>13</v>
+      </c>
+      <c r="F84" t="s">
+        <v>359</v>
+      </c>
+      <c r="G84" t="s">
+        <v>15</v>
+      </c>
+      <c r="H84" t="s">
+        <v>114</v>
+      </c>
+      <c r="I84" t="s">
+        <v>360</v>
+      </c>
+      <c r="J84" t="s">
+        <v>361</v>
+      </c>
+      <c r="K84" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>363</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85" t="s">
+        <v>13</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
+        <v>364</v>
+      </c>
+      <c r="G85" t="s">
+        <v>15</v>
+      </c>
+      <c r="H85" t="s">
+        <v>114</v>
+      </c>
+      <c r="I85" t="s">
+        <v>365</v>
+      </c>
+      <c r="J85" t="s">
+        <v>366</v>
+      </c>
+      <c r="K85" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>368</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86" t="s">
+        <v>13</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>13</v>
+      </c>
+      <c r="F86" t="s">
+        <v>369</v>
+      </c>
+      <c r="G86" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" t="s">
+        <v>114</v>
+      </c>
+      <c r="I86" t="s">
+        <v>370</v>
+      </c>
+      <c r="J86" t="s">
+        <v>283</v>
+      </c>
+      <c r="K86" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>372</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>13</v>
+      </c>
+      <c r="F87" t="s">
+        <v>373</v>
+      </c>
+      <c r="G87" t="s">
+        <v>15</v>
+      </c>
+      <c r="H87" t="s">
+        <v>114</v>
+      </c>
+      <c r="I87" t="s">
+        <v>374</v>
+      </c>
+      <c r="J87" t="s">
+        <v>375</v>
+      </c>
+      <c r="K87" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>377</v>
+      </c>
+      <c r="B88" t="s">
+        <v>12</v>
+      </c>
+      <c r="C88" t="s">
+        <v>13</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>378</v>
+      </c>
+      <c r="G88" t="s">
+        <v>15</v>
+      </c>
+      <c r="H88" t="s">
+        <v>114</v>
+      </c>
+      <c r="I88" t="s">
+        <v>379</v>
+      </c>
+      <c r="J88" t="s">
+        <v>356</v>
+      </c>
+      <c r="K88" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>380</v>
+      </c>
+      <c r="B89" t="s">
+        <v>191</v>
+      </c>
+      <c r="C89" t="s">
+        <v>13</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="E89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>381</v>
+      </c>
+      <c r="G89" t="s">
+        <v>15</v>
+      </c>
+      <c r="H89" t="s">
+        <v>114</v>
+      </c>
+      <c r="I89" t="s">
+        <v>382</v>
+      </c>
+      <c r="J89" t="s">
+        <v>361</v>
+      </c>
+      <c r="K89" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>383</v>
+      </c>
+      <c r="B90" t="s">
+        <v>12</v>
+      </c>
+      <c r="C90" t="s">
+        <v>13</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>384</v>
+      </c>
+      <c r="G90" t="s">
+        <v>15</v>
+      </c>
+      <c r="H90" t="s">
+        <v>114</v>
+      </c>
+      <c r="I90" t="s">
+        <v>385</v>
+      </c>
+      <c r="J90" t="s">
+        <v>366</v>
+      </c>
+      <c r="K90" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>386</v>
+      </c>
+      <c r="B91" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" t="s">
+        <v>13</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>387</v>
+      </c>
+      <c r="G91" t="s">
+        <v>15</v>
+      </c>
+      <c r="H91" t="s">
+        <v>114</v>
+      </c>
+      <c r="I91" t="s">
+        <v>388</v>
+      </c>
+      <c r="J91" t="s">
+        <v>283</v>
+      </c>
+      <c r="K91" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>389</v>
+      </c>
+      <c r="B92" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" t="s">
+        <v>13</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="s">
+        <v>13</v>
+      </c>
+      <c r="F92" t="s">
+        <v>390</v>
+      </c>
+      <c r="G92" t="s">
+        <v>15</v>
+      </c>
+      <c r="H92" t="s">
+        <v>114</v>
+      </c>
+      <c r="I92" t="s">
+        <v>391</v>
+      </c>
+      <c r="J92" t="s">
+        <v>375</v>
+      </c>
+      <c r="K92" t="s">
+        <v>376</v>
       </c>
     </row>
   </sheetData>
